--- a/data/legacy-xlsx/Res Filiformes.xlsx
+++ b/data/legacy-xlsx/Res Filiformes.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="AMOR" sheetId="1" state="visible" r:id="rId2"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="232">
   <si>
     <t xml:space="preserve">идиомы/конструкции</t>
   </si>
@@ -391,9 +391,6 @@
 4 el hilo conductor es el amor</t>
   </si>
   <si>
-    <t xml:space="preserve">nos amarramos a un amor a la vida superior a la Creación,</t>
-  </si>
-  <si>
     <t xml:space="preserve">GT</t>
   </si>
   <si>
@@ -798,9 +795,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">de pronto irrumpe una alborada contra la desilusión apaciguando la sonoridad de la tristeza que teje el poema " VE</t>
-  </si>
-  <si>
     <t xml:space="preserve">1  El brasileño no lo pensó dos veces y cruzó un tremendo zurdazo, desatando la tristeza en todo el estadio holandés.
 2  le contó que está profundamente enamorado de Bárbara, desatando su tristeza y molestia
 3 lo que desató la tristeza de los seguidores de la producción de Meg
@@ -1198,7 +1192,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1315,12 +1309,6 @@
       <name val="Times New Roman"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1616,7 +1604,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1814,11 +1802,11 @@
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="29.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="31.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.93"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="8" style="1" width="12.63"/>
   </cols>
   <sheetData>
@@ -2016,13 +2004,11 @@
       <c r="G10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="I10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -2033,7 +2019,7 @@
     </row>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -2044,32 +2030,32 @@
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="E13" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>62</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -2078,10 +2064,10 @@
     </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -2091,13 +2077,13 @@
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -2106,25 +2092,25 @@
     </row>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -2134,11 +2120,11 @@
     </row>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -2147,13 +2133,13 @@
     </row>
     <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -2162,44 +2148,44 @@
     </row>
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="E22" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="G22" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5175,10 +5161,10 @@
   <sheetData>
     <row r="1" s="16" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>90</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>91</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>2</v>
@@ -5187,13 +5173,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H1" s="14"/>
       <c r="I1" s="15" t="s">
@@ -5223,10 +5209,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>95</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="19"/>
@@ -5238,10 +5224,10 @@
         <v>15</v>
       </c>
       <c r="B3" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>96</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>97</v>
       </c>
       <c r="D3" s="20"/>
       <c r="E3" s="19"/>
@@ -5253,15 +5239,15 @@
         <v>17</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>98</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>99</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="19"/>
       <c r="F4" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5269,17 +5255,17 @@
         <v>22</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" s="20"/>
       <c r="E5" s="22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I5" s="0"/>
     </row>
@@ -5298,10 +5284,10 @@
         <v>31</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="19"/>
@@ -5312,11 +5298,11 @@
         <v>36</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
@@ -5326,10 +5312,10 @@
         <v>41</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19"/>
@@ -5340,25 +5326,25 @@
         <v>45</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>107</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>108</v>
       </c>
       <c r="E10" s="19"/>
       <c r="F10" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
@@ -5367,10 +5353,10 @@
     </row>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
@@ -5379,41 +5365,41 @@
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>112</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>113</v>
       </c>
       <c r="E13" s="19"/>
       <c r="F13" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="19"/>
       <c r="F14" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="20"/>
@@ -5423,13 +5409,13 @@
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>114</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>115</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="19"/>
@@ -5437,11 +5423,11 @@
     </row>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="19"/>
@@ -5449,7 +5435,7 @@
     </row>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -5459,19 +5445,19 @@
     </row>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
       <c r="D19" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20"/>
@@ -5481,41 +5467,41 @@
     </row>
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="18" t="s">
         <v>117</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>118</v>
       </c>
       <c r="E21" s="19"/>
       <c r="F21" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>121</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>122</v>
       </c>
       <c r="E22" s="19"/>
       <c r="F22" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -5538,7 +5524,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.74"/>
@@ -5549,10 +5535,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="24" t="s">
         <v>123</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>124</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>2</v>
@@ -5567,7 +5553,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I1" s="26" t="s">
         <v>7</v>
@@ -5578,15 +5564,15 @@
         <v>8</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D2" s="29"/>
       <c r="E2" s="28"/>
       <c r="F2" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5594,7 +5580,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C3" s="31"/>
       <c r="D3" s="32"/>
@@ -5606,10 +5592,10 @@
         <v>17</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D4" s="29"/>
       <c r="E4" s="28"/>
@@ -5620,15 +5606,15 @@
         <v>22</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" s="32"/>
       <c r="E5" s="33"/>
       <c r="F5" s="34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5636,10 +5622,10 @@
         <v>28</v>
       </c>
       <c r="B6" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="28" t="s">
         <v>132</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>133</v>
       </c>
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
@@ -5650,13 +5636,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C7" s="31"/>
       <c r="D7" s="32"/>
       <c r="E7" s="31"/>
       <c r="F7" s="32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5664,15 +5650,15 @@
         <v>36</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" s="29"/>
       <c r="E8" s="29"/>
       <c r="F8" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5680,10 +5666,10 @@
         <v>41</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" s="31"/>
       <c r="E9" s="31"/>
@@ -5694,24 +5680,24 @@
         <v>45</v>
       </c>
       <c r="B10" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>137</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>138</v>
       </c>
       <c r="D10" s="28"/>
       <c r="E10" s="28"/>
       <c r="F10" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I10" s="35"/>
     </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
@@ -5720,13 +5706,13 @@
     </row>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" s="29"/>
       <c r="E12" s="29"/>
@@ -5734,29 +5720,29 @@
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="36" t="s">
         <v>140</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>141</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="31"/>
       <c r="F13" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D14" s="29"/>
       <c r="E14" s="28"/>
@@ -5764,13 +5750,13 @@
     </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D15" s="32"/>
       <c r="E15" s="31"/>
@@ -5778,45 +5764,45 @@
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D16" s="29"/>
       <c r="E16" s="28"/>
       <c r="F16" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D17" s="32"/>
       <c r="E17" s="31"/>
       <c r="F17" s="32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D18" s="29"/>
       <c r="E18" s="29"/>
@@ -5824,10 +5810,10 @@
     </row>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C19" s="31"/>
       <c r="D19" s="32"/>
@@ -5836,13 +5822,13 @@
     </row>
     <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D20" s="29"/>
       <c r="E20" s="28"/>
@@ -5850,36 +5836,36 @@
     </row>
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" s="32"/>
       <c r="E21" s="31"/>
       <c r="F21" s="32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="40" t="s">
         <v>148</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" s="40" t="s">
-        <v>149</v>
       </c>
       <c r="E22" s="28"/>
       <c r="F22" s="32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -5902,7 +5888,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA22"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="19"/>
@@ -5913,13 +5899,13 @@
   <sheetData>
     <row r="1" s="45" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="42" t="s">
         <v>150</v>
-      </c>
-      <c r="C1" s="42" t="s">
-        <v>151</v>
       </c>
       <c r="D1" s="42" t="s">
         <v>3</v>
@@ -5931,12 +5917,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H1" s="43"/>
-      <c r="I1" s="44" t="s">
-        <v>7</v>
-      </c>
+      <c r="I1" s="44"/>
       <c r="J1" s="43"/>
       <c r="K1" s="43"/>
       <c r="L1" s="43"/>
@@ -5961,18 +5945,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="48" t="s">
         <v>152</v>
-      </c>
-      <c r="C2" s="48" t="s">
-        <v>153</v>
       </c>
       <c r="D2" s="48"/>
       <c r="E2" s="48"/>
       <c r="F2" s="48"/>
       <c r="G2" s="48"/>
-      <c r="I2" s="49" t="s">
-        <v>154</v>
-      </c>
+      <c r="I2" s="49"/>
     </row>
     <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="46" t="s">
@@ -5990,7 +5972,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -6003,16 +5985,16 @@
         <v>22</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D5" s="48"/>
       <c r="E5" s="48"/>
       <c r="F5" s="50"/>
       <c r="G5" s="48" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6031,7 +6013,7 @@
         <v>31</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C7" s="48"/>
       <c r="D7" s="48"/>
@@ -6066,24 +6048,24 @@
         <v>45</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
       <c r="F10" s="47"/>
       <c r="G10" s="48" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -6093,7 +6075,7 @@
     </row>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
@@ -6104,24 +6086,24 @@
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C13" s="48"/>
       <c r="D13" s="48"/>
       <c r="E13" s="48"/>
       <c r="F13" s="48" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G13" s="47" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
@@ -6132,7 +6114,7 @@
     </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="48"/>
       <c r="C15" s="48"/>
@@ -6143,10 +6125,10 @@
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C16" s="48"/>
       <c r="D16" s="48"/>
@@ -6156,10 +6138,10 @@
     </row>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
@@ -6169,7 +6151,7 @@
     </row>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
@@ -6180,7 +6162,7 @@
     </row>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
@@ -6191,7 +6173,7 @@
     </row>
     <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" s="50"/>
       <c r="C20" s="48"/>
@@ -6202,7 +6184,7 @@
     </row>
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21" s="48"/>
       <c r="C21" s="48"/>
@@ -6213,13 +6195,13 @@
     </row>
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="46" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D22" s="48"/>
       <c r="E22" s="48"/>
@@ -6246,7 +6228,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.74"/>
@@ -6258,25 +6240,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="D1" s="52" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="E1" s="52" t="s">
         <v>173</v>
-      </c>
-      <c r="D1" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="E1" s="52" t="s">
-        <v>175</v>
       </c>
       <c r="F1" s="52" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6284,15 +6266,15 @@
         <v>8</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D2" s="28"/>
       <c r="E2" s="29"/>
       <c r="F2" s="28" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G2" s="29"/>
     </row>
@@ -6301,18 +6283,18 @@
         <v>15</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D3" s="31"/>
       <c r="E3" s="32"/>
       <c r="F3" s="31" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G3" s="53" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6320,15 +6302,15 @@
         <v>17</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D4" s="28"/>
       <c r="E4" s="29"/>
       <c r="F4" s="28" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G4" s="29"/>
     </row>
@@ -6337,18 +6319,18 @@
         <v>22</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D5" s="31"/>
       <c r="E5" s="32"/>
       <c r="F5" s="33" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6356,10 +6338,10 @@
         <v>28</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D6" s="28"/>
       <c r="E6" s="29"/>
@@ -6371,15 +6353,15 @@
         <v>31</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D7" s="31"/>
       <c r="E7" s="32"/>
       <c r="F7" s="31" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G7" s="32"/>
     </row>
@@ -6388,15 +6370,15 @@
         <v>36</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D8" s="28"/>
       <c r="E8" s="29"/>
       <c r="F8" s="37" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G8" s="29"/>
     </row>
@@ -6405,17 +6387,17 @@
         <v>41</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D9" s="31"/>
       <c r="E9" s="31" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G9" s="32"/>
     </row>
@@ -6424,28 +6406,28 @@
         <v>45</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D10" s="28"/>
       <c r="E10" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="G10" s="37" t="s">
         <v>205</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
@@ -6455,10 +6437,10 @@
     </row>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C12" s="29"/>
       <c r="D12" s="29"/>
@@ -6468,92 +6450,92 @@
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
       <c r="E13" s="32"/>
       <c r="F13" s="31" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C14" s="29"/>
       <c r="D14" s="29"/>
       <c r="E14" s="29"/>
       <c r="F14" s="28" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G14" s="29"/>
     </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
       <c r="E15" s="32"/>
       <c r="F15" s="31" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G15" s="32"/>
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D16" s="28"/>
       <c r="E16" s="29"/>
       <c r="F16" s="28" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G16" s="29"/>
     </row>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D17" s="31"/>
       <c r="E17" s="32"/>
       <c r="F17" s="31" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G17" s="32"/>
     </row>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="29"/>
@@ -6562,65 +6544,65 @@
     </row>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D19" s="31"/>
       <c r="E19" s="32"/>
       <c r="F19" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G19" s="32"/>
     </row>
     <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C20" s="29"/>
       <c r="D20" s="29"/>
       <c r="E20" s="29"/>
       <c r="F20" s="28" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G20" s="29"/>
     </row>
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32"/>
       <c r="F21" s="31" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G21" s="32"/>
     </row>
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D22" s="28"/>
       <c r="E22" s="29"/>
       <c r="F22" s="28" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G22" s="29"/>
     </row>
